--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8780,6 +8780,27 @@
       <c r="E398" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>335.22</v>
+      </c>
+      <c r="C399" t="n">
+        <v>332.59</v>
+      </c>
+      <c r="D399" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B420"/>
+  <dimension ref="A1:B421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12997,6 +13018,16 @@
       </c>
       <c r="B420" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -13165,28 +13196,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5500764331543071</v>
+        <v>-0.5467138773514575</v>
       </c>
       <c r="J2" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1211427121101228</v>
+        <v>0.1202650004359694</v>
       </c>
       <c r="M2" t="n">
-        <v>8.670467021690989</v>
+        <v>8.663056092050992</v>
       </c>
       <c r="N2" t="n">
-        <v>121.7769988491524</v>
+        <v>121.5928333115826</v>
       </c>
       <c r="O2" t="n">
-        <v>11.03526161217542</v>
+        <v>11.0269140429942</v>
       </c>
       <c r="P2" t="n">
-        <v>342.6167914403206</v>
+        <v>342.5816141129121</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13243,28 +13274,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04923763054835437</v>
+        <v>-0.04832684241266648</v>
       </c>
       <c r="J3" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K3" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004716957961504731</v>
+        <v>0.0004566795150768854</v>
       </c>
       <c r="M3" t="n">
-        <v>7.130195690511347</v>
+        <v>7.115149727823547</v>
       </c>
       <c r="N3" t="n">
-        <v>287.7157673364528</v>
+        <v>286.9984910467658</v>
       </c>
       <c r="O3" t="n">
-        <v>16.96218639611217</v>
+        <v>16.94102981069232</v>
       </c>
       <c r="P3" t="n">
-        <v>331.958876938739</v>
+        <v>331.949422607124</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13321,28 +13352,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1779071988387371</v>
+        <v>-0.1774417615246567</v>
       </c>
       <c r="J4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K4" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09811488739889551</v>
+        <v>0.09807934125118156</v>
       </c>
       <c r="M4" t="n">
-        <v>3.127855274982696</v>
+        <v>3.122164576277595</v>
       </c>
       <c r="N4" t="n">
-        <v>16.49392751827026</v>
+        <v>16.45494803253362</v>
       </c>
       <c r="O4" t="n">
-        <v>4.061271662702492</v>
+        <v>4.056469897895659</v>
       </c>
       <c r="P4" t="n">
-        <v>395.8999445869162</v>
+        <v>395.8951595125272</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13380,7 +13411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24105,6 +24136,33 @@
         </is>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>-42.80167771256336,173.36250111714375</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>-42.80198712069021,173.36167389715027</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>-42.80284477907083,173.36161738855736</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8801,6 +8801,27 @@
       <c r="E399" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="C400" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="D400" t="n">
+        <v>392.86</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B421"/>
+  <dimension ref="A1:B423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13028,6 +13049,26 @@
       </c>
       <c r="B421" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -13196,28 +13237,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5467138773514575</v>
+        <v>-0.5432564188678241</v>
       </c>
       <c r="J2" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1202650004359694</v>
+        <v>0.1193483634694804</v>
       </c>
       <c r="M2" t="n">
-        <v>8.663056092050992</v>
+        <v>8.655939353191684</v>
       </c>
       <c r="N2" t="n">
-        <v>121.5928333115826</v>
+        <v>121.4159900986071</v>
       </c>
       <c r="O2" t="n">
-        <v>11.0269140429942</v>
+        <v>11.01889241705386</v>
       </c>
       <c r="P2" t="n">
-        <v>342.5816141129121</v>
+        <v>342.5452535976924</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13274,28 +13315,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04832684241266648</v>
+        <v>-0.04736527029334907</v>
       </c>
       <c r="J3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K3" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004566795150768854</v>
+        <v>0.0004409036870554051</v>
       </c>
       <c r="M3" t="n">
-        <v>7.115149727823547</v>
+        <v>7.100348967212073</v>
       </c>
       <c r="N3" t="n">
-        <v>286.9984910467658</v>
+        <v>286.2858316686614</v>
       </c>
       <c r="O3" t="n">
-        <v>16.94102981069232</v>
+        <v>16.91998320533036</v>
       </c>
       <c r="P3" t="n">
-        <v>331.949422607124</v>
+        <v>331.9393882892551</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13352,28 +13393,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1774417615246567</v>
+        <v>-0.1766718161639695</v>
       </c>
       <c r="J4" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K4" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09807934125118156</v>
+        <v>0.09772038652663506</v>
       </c>
       <c r="M4" t="n">
-        <v>3.122164576277595</v>
+        <v>3.117882867836338</v>
       </c>
       <c r="N4" t="n">
-        <v>16.45494803253362</v>
+        <v>16.42039247813118</v>
       </c>
       <c r="O4" t="n">
-        <v>4.056469897895659</v>
+        <v>4.052208345844421</v>
       </c>
       <c r="P4" t="n">
-        <v>395.8951595125272</v>
+        <v>395.8872015898581</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13411,7 +13452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24163,6 +24204,33 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-42.80167912886079,173.36250218781782</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-42.80198789029498,173.36167474410456</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-42.80284849792447,173.3616232070592</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8822,6 +8822,27 @@
       <c r="E400" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>334.78</v>
+      </c>
+      <c r="C401" t="n">
+        <v>334.63</v>
+      </c>
+      <c r="D401" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13069,6 +13090,16 @@
       </c>
       <c r="B423" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -13237,28 +13268,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5432564188678241</v>
+        <v>-0.5400834967772802</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K2" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1193483634694804</v>
+        <v>0.1185633978987661</v>
       </c>
       <c r="M2" t="n">
-        <v>8.655939353191684</v>
+        <v>8.647503082590589</v>
       </c>
       <c r="N2" t="n">
-        <v>121.4159900986071</v>
+        <v>121.218827827355</v>
       </c>
       <c r="O2" t="n">
-        <v>11.01889241705386</v>
+        <v>11.00994222634047</v>
       </c>
       <c r="P2" t="n">
-        <v>342.5452535976924</v>
+        <v>342.5117130030112</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13315,28 +13346,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04736527029334907</v>
+        <v>-0.04548638945605963</v>
       </c>
       <c r="J3" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K3" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004409036870554051</v>
+        <v>0.0004086601196452433</v>
       </c>
       <c r="M3" t="n">
-        <v>7.100348967212073</v>
+        <v>7.088593135530769</v>
       </c>
       <c r="N3" t="n">
-        <v>286.2858316686614</v>
+        <v>285.6053821196815</v>
       </c>
       <c r="O3" t="n">
-        <v>16.91998320533036</v>
+        <v>16.89986337576968</v>
       </c>
       <c r="P3" t="n">
-        <v>331.9393882892551</v>
+        <v>331.919679667896</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13393,28 +13424,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1766718161639695</v>
+        <v>-0.1753461266846461</v>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09772038652663506</v>
+        <v>0.09673979326547133</v>
       </c>
       <c r="M4" t="n">
-        <v>3.117882867836338</v>
+        <v>3.116115155459311</v>
       </c>
       <c r="N4" t="n">
-        <v>16.42039247813118</v>
+        <v>16.39900614998456</v>
       </c>
       <c r="O4" t="n">
-        <v>4.052208345844421</v>
+        <v>4.049568637519872</v>
       </c>
       <c r="P4" t="n">
-        <v>395.8872015898581</v>
+        <v>395.8734278400098</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13452,7 +13483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24231,6 +24262,33 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-42.80167425050288,173.36249849994064</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-42.80200139335945,173.3616896043065</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-42.80285540436613,173.3616340128502</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8841,6 +8841,48 @@
         <v>394.03</v>
       </c>
       <c r="E401" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>336.52</v>
+      </c>
+      <c r="C402" t="n">
+        <v>334.67</v>
+      </c>
+      <c r="D402" t="n">
+        <v>393.92</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>335.67</v>
+      </c>
+      <c r="C403" t="n">
+        <v>335.86</v>
+      </c>
+      <c r="D403" t="n">
+        <v>393.9</v>
+      </c>
+      <c r="E403" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8857,7 +8899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13100,6 +13142,26 @@
       </c>
       <c r="B424" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -13268,28 +13330,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5400834967772802</v>
+        <v>-0.5325575606500677</v>
       </c>
       <c r="J2" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K2" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1185633978987661</v>
+        <v>0.1164470830888613</v>
       </c>
       <c r="M2" t="n">
-        <v>8.647503082590589</v>
+        <v>8.635975537187068</v>
       </c>
       <c r="N2" t="n">
-        <v>121.218827827355</v>
+        <v>120.9202118105425</v>
       </c>
       <c r="O2" t="n">
-        <v>11.00994222634047</v>
+        <v>10.99637266604504</v>
       </c>
       <c r="P2" t="n">
-        <v>342.5117130030112</v>
+        <v>342.431918290238</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13346,28 +13408,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04548638945605963</v>
+        <v>-0.04119420195680195</v>
       </c>
       <c r="J3" t="n">
+        <v>402</v>
+      </c>
+      <c r="K3" t="n">
         <v>400</v>
       </c>
-      <c r="K3" t="n">
-        <v>398</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0004086601196452433</v>
+        <v>0.0003385104054293153</v>
       </c>
       <c r="M3" t="n">
-        <v>7.088593135530769</v>
+        <v>7.067640932808169</v>
       </c>
       <c r="N3" t="n">
-        <v>285.6053821196815</v>
+        <v>284.2810473933397</v>
       </c>
       <c r="O3" t="n">
-        <v>16.89986337576968</v>
+        <v>16.86063603169642</v>
       </c>
       <c r="P3" t="n">
-        <v>331.919679667896</v>
+        <v>331.8745119992897</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13424,28 +13486,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1753461266846461</v>
+        <v>-0.1728353685482575</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09673979326547133</v>
+        <v>0.09493218365290457</v>
       </c>
       <c r="M4" t="n">
-        <v>3.116115155459311</v>
+        <v>3.111907737465266</v>
       </c>
       <c r="N4" t="n">
-        <v>16.39900614998456</v>
+        <v>16.35288463025441</v>
       </c>
       <c r="O4" t="n">
-        <v>4.049568637519872</v>
+        <v>4.04387000659695</v>
       </c>
       <c r="P4" t="n">
-        <v>395.8734278400098</v>
+        <v>395.847260508089</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13483,7 +13545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24289,6 +24351,60 @@
         </is>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-42.80168794137799,173.36250884979106</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-42.80200167321567,173.36168991229002</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-42.802854755042596,173.36163299692103</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-42.80168125330694,173.36250379382906</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-42.80200999893835,173.36169907480127</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-42.80285463698377,173.36163281220664</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8883,6 +8883,69 @@
         <v>393.9</v>
       </c>
       <c r="E403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="C404" t="n">
+        <v>334.81</v>
+      </c>
+      <c r="D404" t="n">
+        <v>393.93</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>331.49</v>
+      </c>
+      <c r="C405" t="n">
+        <v>334.13</v>
+      </c>
+      <c r="D405" t="n">
+        <v>393.07</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="C406" t="n">
+        <v>333.17</v>
+      </c>
+      <c r="D406" t="n">
+        <v>393.47</v>
+      </c>
+      <c r="E406" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8899,7 +8962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B426"/>
+  <dimension ref="A1:B429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13162,6 +13225,36 @@
       </c>
       <c r="B426" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -13330,28 +13423,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5325575606500677</v>
+        <v>-0.5285183190986207</v>
       </c>
       <c r="J2" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="K2" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1164470830888613</v>
+        <v>0.1163586653307825</v>
       </c>
       <c r="M2" t="n">
-        <v>8.635975537187068</v>
+        <v>8.589613976351103</v>
       </c>
       <c r="N2" t="n">
-        <v>120.9202118105425</v>
+        <v>120.116296766451</v>
       </c>
       <c r="O2" t="n">
-        <v>10.99637266604504</v>
+        <v>10.95975806149255</v>
       </c>
       <c r="P2" t="n">
-        <v>342.431918290238</v>
+        <v>342.3889441652676</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13408,28 +13501,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04119420195680195</v>
+        <v>-0.03665374910571236</v>
       </c>
       <c r="J3" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="K3" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003385104054293153</v>
+        <v>0.0002720355280598774</v>
       </c>
       <c r="M3" t="n">
-        <v>7.067640932808169</v>
+        <v>7.030518725694584</v>
       </c>
       <c r="N3" t="n">
-        <v>284.2810473933397</v>
+        <v>282.245375370226</v>
       </c>
       <c r="O3" t="n">
-        <v>16.86063603169642</v>
+        <v>16.80015998049501</v>
       </c>
       <c r="P3" t="n">
-        <v>331.8745119992897</v>
+        <v>331.826551109417</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13486,28 +13579,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1728353685482575</v>
+        <v>-0.1697442988139117</v>
       </c>
       <c r="J4" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="K4" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09493218365290457</v>
+        <v>0.092950088727764</v>
       </c>
       <c r="M4" t="n">
-        <v>3.111907737465266</v>
+        <v>3.102767950079207</v>
       </c>
       <c r="N4" t="n">
-        <v>16.35288463025441</v>
+        <v>16.26900930785934</v>
       </c>
       <c r="O4" t="n">
-        <v>4.04387000659695</v>
+        <v>4.033485999462418</v>
       </c>
       <c r="P4" t="n">
-        <v>395.847260508089</v>
+        <v>395.8149143561185</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13545,7 +13638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24405,6 +24498,87 @@
         </is>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-42.80166646086661,173.36249261123467</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-42.8020026527125,173.36169099023238</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-42.802854814072006,173.36163308927823</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-42.80164836373061,173.3624789304084</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-42.801997895156404,173.36168575451262</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-42.80284973754227,173.36162514656</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>-42.801621847489066,173.36245888503825</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>-42.8019911786062,173.36167836290963</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>-42.802852098718965,173.36162884084737</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E406"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8946,6 +8946,48 @@
         <v>393.47</v>
       </c>
       <c r="E406" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>320.98</v>
+      </c>
+      <c r="C407" t="n">
+        <v>332.19</v>
+      </c>
+      <c r="D407" t="n">
+        <v>393.21</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="C408" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="D408" t="n">
+        <v>392.49</v>
+      </c>
+      <c r="E408" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8962,7 +9004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B429"/>
+  <dimension ref="A1:B431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13255,6 +13297,26 @@
       </c>
       <c r="B429" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -13423,28 +13485,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5285183190986207</v>
+        <v>-0.5385359172822037</v>
       </c>
       <c r="J2" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K2" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1163586653307825</v>
+        <v>0.1207792235454326</v>
       </c>
       <c r="M2" t="n">
-        <v>8.589613976351103</v>
+        <v>8.609758450675846</v>
       </c>
       <c r="N2" t="n">
-        <v>120.116296766451</v>
+        <v>120.1480835644412</v>
       </c>
       <c r="O2" t="n">
-        <v>10.95975806149255</v>
+        <v>10.96120812522238</v>
       </c>
       <c r="P2" t="n">
-        <v>342.3889441652676</v>
+        <v>342.4958850617616</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13501,28 +13563,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03665374910571236</v>
+        <v>-0.03524774669663178</v>
       </c>
       <c r="J3" t="n">
+        <v>407</v>
+      </c>
+      <c r="K3" t="n">
         <v>405</v>
       </c>
-      <c r="K3" t="n">
-        <v>403</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0002720355280598774</v>
+        <v>0.000254077689973653</v>
       </c>
       <c r="M3" t="n">
-        <v>7.030518725694584</v>
+        <v>7.000552024508954</v>
       </c>
       <c r="N3" t="n">
-        <v>282.245375370226</v>
+        <v>280.863089791771</v>
       </c>
       <c r="O3" t="n">
-        <v>16.80015998049501</v>
+        <v>16.75897042755822</v>
       </c>
       <c r="P3" t="n">
-        <v>331.826551109417</v>
+        <v>331.811657776793</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13579,28 +13641,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1697442988139117</v>
+        <v>-0.16832206244206</v>
       </c>
       <c r="J4" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K4" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.092950088727764</v>
+        <v>0.09230473585717658</v>
       </c>
       <c r="M4" t="n">
-        <v>3.102767950079207</v>
+        <v>3.093946455666728</v>
       </c>
       <c r="N4" t="n">
-        <v>16.26900930785934</v>
+        <v>16.20150742916331</v>
       </c>
       <c r="O4" t="n">
-        <v>4.033485999462418</v>
+        <v>4.025109617036946</v>
       </c>
       <c r="P4" t="n">
-        <v>395.8149143561185</v>
+        <v>395.7999937042644</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13638,7 +13700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E406"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24579,6 +24641,60 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>-42.80156566766544,173.3624164150823</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>-42.801984322127346,173.36167081731654</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>-42.80285056395413,173.36162643956055</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-42.80151114017369,173.36237519431637</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-42.801986910798,173.36167366616272</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-42.802846313835865,173.36161978984376</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0405/nzd0405.xlsx
+++ b/data/nzd0405/nzd0405.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E408"/>
+  <dimension ref="A1:E409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8988,6 +8988,27 @@
         <v>392.49</v>
       </c>
       <c r="E408" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>311.2</v>
+      </c>
+      <c r="C409" t="n">
+        <v>332.09</v>
+      </c>
+      <c r="D409" t="n">
+        <v>392</v>
+      </c>
+      <c r="E409" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9004,7 +9025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B431"/>
+  <dimension ref="A1:B432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13317,6 +13338,16 @@
       </c>
       <c r="B431" t="n">
         <v>0.37</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -13485,28 +13516,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5385359172822037</v>
+        <v>-0.5463881650659068</v>
       </c>
       <c r="J2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1207792235454326</v>
+        <v>0.1237992092369229</v>
       </c>
       <c r="M2" t="n">
-        <v>8.609758450675846</v>
+        <v>8.638380291058594</v>
       </c>
       <c r="N2" t="n">
-        <v>120.1480835644412</v>
+        <v>120.5508609778614</v>
       </c>
       <c r="O2" t="n">
-        <v>10.96120812522238</v>
+        <v>10.97956560970703</v>
       </c>
       <c r="P2" t="n">
-        <v>342.4958850617616</v>
+        <v>342.58008117371</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13563,28 +13594,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03524774669663178</v>
+        <v>-0.03468440683193728</v>
       </c>
       <c r="J3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K3" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000254077689973653</v>
+        <v>0.0002472518758057651</v>
       </c>
       <c r="M3" t="n">
-        <v>7.000552024508954</v>
+        <v>6.985194745002886</v>
       </c>
       <c r="N3" t="n">
-        <v>280.863089791771</v>
+        <v>280.174958020217</v>
       </c>
       <c r="O3" t="n">
-        <v>16.75897042755822</v>
+        <v>16.7384275850576</v>
       </c>
       <c r="P3" t="n">
-        <v>331.811657776793</v>
+        <v>331.8056633234949</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13641,28 +13672,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.16832206244206</v>
+        <v>-0.1680003242080292</v>
       </c>
       <c r="J4" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K4" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09230473585717658</v>
+        <v>0.09239478841185</v>
       </c>
       <c r="M4" t="n">
-        <v>3.093946455666728</v>
+        <v>3.087800146086772</v>
       </c>
       <c r="N4" t="n">
-        <v>16.20150742916331</v>
+        <v>16.16300766763452</v>
       </c>
       <c r="O4" t="n">
-        <v>4.025109617036946</v>
+        <v>4.020324323687645</v>
       </c>
       <c r="P4" t="n">
-        <v>395.7999937042644</v>
+        <v>395.7966022243011</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13700,7 +13731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E408"/>
+  <dimension ref="A1:E409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24695,6 +24726,33 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-42.801488715443114,173.36235824207444</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-42.80198362248663,173.36167004735816</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-42.802843421394044,173.36161526434256</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
